--- a/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
+++ b/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="b">
         <v>1</v>
       </c>
@@ -569,7 +568,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="b">
         <v>1</v>
       </c>
@@ -616,7 +614,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="b">
         <v>1</v>
       </c>
@@ -663,7 +660,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="b">
         <v>1</v>
       </c>
@@ -710,7 +706,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="b">
         <v>1</v>
       </c>
@@ -757,7 +752,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="b">
         <v>1</v>
       </c>
@@ -806,7 +800,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="b">
         <v>1</v>
       </c>
@@ -853,7 +846,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="b">
         <v>1</v>
       </c>
@@ -900,7 +892,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="b">
         <v>1</v>
       </c>
@@ -947,7 +938,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
@@ -994,7 +984,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>
@@ -1041,7 +1030,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="b">
         <v>1</v>
       </c>
@@ -1088,7 +1076,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="b">
         <v>1</v>
       </c>
@@ -1137,7 +1124,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="b">
         <v>1</v>
       </c>
@@ -1186,7 +1172,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="b">
         <v>1</v>
       </c>
@@ -1235,7 +1220,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="b">
         <v>1</v>
       </c>
@@ -1284,7 +1268,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="b">
         <v>1</v>
       </c>
@@ -1331,7 +1314,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="b">
         <v>1</v>
       </c>
@@ -1378,7 +1360,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="b">
         <v>1</v>
       </c>
@@ -1425,7 +1406,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="b">
         <v>1</v>
       </c>
@@ -1472,7 +1452,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="b">
         <v>1</v>
       </c>
@@ -1519,7 +1498,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="b">
         <v>1</v>
       </c>
@@ -1566,7 +1544,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="b">
         <v>1</v>
       </c>
@@ -1613,7 +1590,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="b">
         <v>1</v>
       </c>
@@ -1713,7 +1689,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="b">
         <v>1</v>
       </c>
@@ -1760,7 +1735,6 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="b">
         <v>1</v>
       </c>
@@ -1809,7 +1783,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="b">
         <v>1</v>
       </c>
@@ -1856,7 +1829,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="b">
         <v>1</v>
       </c>
@@ -1903,7 +1875,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="b">
         <v>1</v>
       </c>
@@ -1952,7 +1923,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="b">
         <v>1</v>
       </c>
@@ -2001,7 +1971,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="b">
         <v>1</v>
       </c>
@@ -2048,7 +2017,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="b">
         <v>1</v>
       </c>
@@ -2097,7 +2065,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="b">
         <v>1</v>
       </c>
@@ -2146,7 +2113,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="b">
         <v>1</v>
       </c>
@@ -2193,7 +2159,6 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="b">
         <v>1</v>
       </c>
@@ -2242,13 +2207,311 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Audited against FAISS docstore on 2026-04-02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QQ038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>What was Tanzania's GDP growth rate in 2023?</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Out-of-country; KNBS Kenya corpus only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QQ039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>How does Uganda's inflation compare to Kenya's in 2024?</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Out-of-country comparison; Uganda data is outside the KNBS Kenya corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QQ040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>What is the poverty rate in Ethiopia as of 2022?</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Out-of-country; Ethiopia data is outside the KNBS Kenya corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QQ041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>What was Kenya's inflation rate in December 2026?</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Future unavailable data; December 2026 CPI is not published in the corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QQ042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>What are the results of the 2029 Kenya Census?</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Future unavailable data; 2029 Kenya Census does not exist in the corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QQ043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Should Kenya reduce interest rates to control inflation?</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Policy recommendation; no official statistical answer expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QQ044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>What policies should KNBS recommend to reduce poverty in Kenya?</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Policy advice; no official statistical answer expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QQ045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Is Kenya's economy performing well compared to its potential?</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Subjective judgment; no single official statistical answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QQ046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Compare Kenya's 2024 CPI inflation with Nigeria's 2024 CPI inflation.</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Cross-country comparison; Nigeria CPI data is outside the KNBS Kenya corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QQ047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>How does Kenya's KDHS 2022 child mortality compare to Rwanda's DHS?</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Cross-country comparison; Rwanda DHS data is outside the KNBS Kenya corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QQ048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the salary of the KNBS Director General?</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Personnel/administrative data; not a KNBS statistical publication answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QQ049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is Kenya's military expenditure as a percentage of GDP in 2024?</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Topic outside indexed KNBS statistical publications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QQ050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>What is the best county in Kenya?</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Subjective/vague; no single official statistical answer.</t>
         </is>
       </c>
     </row>

--- a/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
+++ b/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2515,6 +2515,1158 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QQ051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>What was Kenya's estimated population in 2024?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>52.4 million</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf p.22</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>"Population (Million) 48.8 49.7 50.6 51.5 52.4"</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QQ052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>What was the growth rate of GDP at constant prices in Kenya in 2024?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.7 per cent</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf p.22</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>"Growth of GDP at Constant Prices (Per cent ) (0.3) 7.6 4.9 5.7 4.7"</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QQ053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What was the total wage employment in Kenya's modern sector in 2024?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3,213.8 thousand</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf p.38</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>"Public 884.7 923.0 937.8 992.9 1,023.2 Private 1,858.0 1,983.0 2,077.5 2,145.5 2,190.6 Total 2,742.6 2,906.1 3,015.4 3,138.5 3,213.8"</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QQ054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How many people were employed by the Teachers Service Commission in 2024?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>410.7 thousand</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-Facts-and-Figures.pdf p.38</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>"Teachers Service Commission 331.1 349.9 348.6 390.4 410.7"</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QQ055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How many holiday and business visitors arrived in Kenya in 2024?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1,703,361</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf p.280</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>"Holiday/ Business Visitors 1,239,439 1,420,794 1,462,496 1,754,874 1,562,170 305,924 529,937 979,747 1,428,284 1,703,361"</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QQ056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>What were Kenya's total visitor arrivals in 2024?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2,394,376</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf p.281</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>"Total Arrivals 1,459,466 1,666,047 1,778,425 2,027,723 2,035,441 579,560 871,304 1,540,978 2,086,769 2,394,376"</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QQ057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>How many tonnes of unmilled wheat did Kenya import in 2024?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2,313,985.3 tonnes</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-Statistical-Abstract.pdf p.190</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>"Wheat, unmilled " 1,362,309.1 1,854,953.8 1,736,691.7 1,998,852.1 1,882,399.8 1,889,921.9 1,676,623.9 2,037,036.0 2,313,985.3"</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QQ058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How many tonnes of maize were produced in Kenya according to the 2025 Agriculture Production Report?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4,028,320 tonnes</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.17</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>"In Kenya, maize is the most significant crop, both in terms of cultivated area and total production. It was grown on 2,407,025 hectares and produced 4,028,320 tonnes"</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QQ059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>What was the area under maize cultivation in Kenya in 2024?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2,407,025 hectares</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.17</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>"It was grown on 2,407,025 hectares and produced 4,028,320 tonnes"</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QQ060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>How many tonnes of Irish potatoes were produced in Kenya according to the 2025 Agriculture Production Report?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2,149,979 tonnes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.17</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>"Irish potatoes emerged as the second most productive crop, generating 2,149,979 tonnes from 225,976 hectares"</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QQ061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>What was the construction inflation rate in Kenya in Q4 2024?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Construction-Input-Price-Indices-for-Fourth-Quarter-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Construction-Input-Price-Indices-for-Fourth-Quarter-2024.pdf p.2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>"The construction inflation rate was 0.87 per cent in Q4-2024"</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QQ062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>What share of Kenya's total stock of foreign liabilities came from Europe at the end of 2023?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>United Kingdom accounted for 46.4 per cent and the Netherlands 17.3 per cent of the total stock from Europe</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2024-Foreign-Investment-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2024-Foreign-Investment-Survey-Report.pdf p.8</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>"the United Kingdom and the Netherlands, which accounted for 46.4 per cent and 17.3 per cent, of the total stock of foreign liabilities from Europe, respectively"</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QQ063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>What percentage of Kenya's total foreign liabilities came from Africa at the end of 2023?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>26.4 per cent</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2024-Foreign-Investment-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2024-Foreign-Investment-Survey-Report.pdf p.8</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>"Africa emerged as the second largest source of foreign liabilities, accounting for 26.4 per cent of the total stock of foreign liabilities at the end of 2023"</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QQ064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>What was Kenya's formal financial access rate in 2024?</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>84.8 per cent</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf p.9</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>"Formal financial access increased from 83.7 percent in 2021 to 84.8 percent in 2024"</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QQ065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>What percentage of Kenyans used mobile money daily in 2024?</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>52.6 per cent</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf p.10</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>"52.6 percent of Kenyans now use mobile money daily"</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QQ066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>What percentage of Kenyans were financially healthy in 2024?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>18.3 per cent</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf p.11</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>"Financial health remains low, with 18.3 percent of Kenyans financially healthy compared to 17.1 percent in 2021"</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QQ067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Which county had the highest working population in Kenya as of 2022?</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Nairobi City, with 2,191,913</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2024-Gross-County-Product.pdf</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2024-Gross-County-Product.pdf p.19</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>"Nairobi City has the highest working population, at 2,191,913"</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QQ068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>What was the leading cause of registered health facility deaths in Mombasa County in 2024?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pneumonia (424 deaths)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kenya-Vital-Statistics-Report-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kenya-Vital-Statistics-Report-2024.pdf p.212</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>"001: MOMBASA Rank Cause of Death Total 1 Pneumonia 424"</t>
+        </is>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QQ069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>What was the volume of export traffic through the port of Mombasa in 2023?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4,950 thousand metric tonnes</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2024-Economic-Survey.pdf</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2024-Economic-Survey.pdf p.327</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>"4,950"; "The volume in metric tonnes of export traffic through the port of Mombasa in 2023, a rise from 4,771 thousand metric tonnes recorded in 2022"</t>
+        </is>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QQ070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>What was Kenya's broad money supply (M3) in August 2023?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>KSh 5,774,645 million</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Leading-Economic-Indicators-August-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Leading-Economic-Indicators-August-2024.pdf p.14</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>"August 2,086,516 2,359,553 4,446,069 1,328,576 5,774,645 1.78"</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QQ071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>According to the 2024 FinAccess Survey, which livelihood group had the highest formal financial access rate?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>The employed, at 96.9 per cent</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2024-FinAccess-Household-Survey-Report.pdf p.30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>"The employed and those who own businesses had the highest access to financial services through formal channels at 96.9 percent and 92.3 percent, respectively"</t>
+        </is>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QQ072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>What were the top three export destinations for Kenyan coffee in the 2023/24 coffee year?</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Belgium (16.8%), USA (16.1%), and Germany (11.4%)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.86</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>"the top leading export destinations for Kenyan coffee in the 2023/24 coffee year were Belgium, USA and Germany at 16.8 per cent, 16.1 per cent and 11.4 per cent, respectively"</t>
+        </is>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QQ073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Which county had the largest meat goat population in Kenya in 2024?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Turkana, with 8,625.2 thousand</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.144</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>"Top 10 Meat Goats Rearing Counties, 2024 8,625.2 ... Turkana"</t>
+        </is>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QQ074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>What was the second most widely cultivated crop in Kenya after maize?</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Beans, covering 1,229,611 hectares</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>National-Agriculture-Production-Report-2025.pdf p.17</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>"Beans were the second most widely cultivated crop, covering 1,229,611 hectares and yielding 759,006 tonnes"</t>
+        </is>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
+++ b/tests/accuracy/StatsChat_QA_Verified_Audited.xlsx
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mobile Phone</t>
+          <t>Mobile phone, 94%</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Audited against FAISS docstore on 2026-04-02.</t>
+          <t>Audited against FAISS docstore on 2026-04-02. Gold answer expanded on 2026-04-16 to include the percentage present in source_text so correct model answers with the value score deterministically.</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What share of Kenya's total stock of foreign liabilities came from Europe at the end of 2023?</t>
+          <t>Which European countries accounted for the largest shares of Kenya's foreign liabilities from Europe at the end of 2023, and what were their shares?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex. Query clarified on 2026-04-16 to ask for within-Europe country shares, matching the audited gold answer.</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What was the second most widely cultivated crop in Kenya after maize?</t>
+          <t>What was the second most widely cultivated crop in Kenya after maize, and what area did it cover?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex.</t>
+          <t>Verified against data/json_split indexed chunk on 2026-04-14; drafted by Claude and checked by Codex. Query clarified on 2026-04-16 to ask for the area included in the audited gold answer.</t>
         </is>
       </c>
     </row>
